--- a/6.Gerenciamento de Projeto/Hobby Hub - Planejamento e Controle do Projeto.xlsx
+++ b/6.Gerenciamento de Projeto/Hobby Hub - Planejamento e Controle do Projeto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabio\OneDrive\Desktop\Faculdade\Hobby Hub Projeto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC12069-B8DE-41FD-A503-950A97A65337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DA5878-2A9E-4B5C-B93E-4B075E73D5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{31237A52-FFD1-4E1D-B5BB-391D11929C61}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{31237A52-FFD1-4E1D-B5BB-391D11929C61}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipe" sheetId="1" r:id="rId1"/>
@@ -4738,7 +4738,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="276">
   <si>
     <t>Equipe</t>
   </si>
@@ -5563,9 +5563,6 @@
     <t>UC08 - Manter tags</t>
   </si>
   <si>
-    <t>Protótipo de Arquitetura + UC01 (Cadastrar-se) + UC02 (Realizar Login)</t>
-  </si>
-  <si>
     <t>UC05 (Postar) + UC08 (Manter Tags)</t>
   </si>
   <si>
@@ -5651,6 +5648,12 @@
   </si>
   <si>
     <t>Modelar, Implementar e UC04 - Visualizar perfil de usuários</t>
+  </si>
+  <si>
+    <t>Protótipo de Arquitetura + UC5(Postar)</t>
+  </si>
+  <si>
+    <t>Em execução</t>
   </si>
 </sst>
 </file>
@@ -5853,13 +5856,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -5952,6 +5948,12 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -6187,9 +6189,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="10" applyProtection="1"/>
     <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6336,83 +6338,59 @@
     <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="9" borderId="1" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="171" fontId="27" fillId="11" borderId="1" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="171" fontId="22" fillId="9" borderId="1" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="171" fontId="22" fillId="11" borderId="1" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="8" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="8" xfId="10" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="8" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="170" fontId="22" fillId="0" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="10" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="170" fontId="22" fillId="0" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="12" borderId="0" xfId="10" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="28" fillId="12" borderId="0" xfId="10" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="13" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="12" borderId="0" xfId="10" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="12" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="13" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="13" borderId="9" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="29" fillId="12" borderId="0" xfId="10" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="13" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="15" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="12" borderId="0" xfId="10" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="14" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="14" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="29" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="12" borderId="0" xfId="10" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="12" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="13" borderId="6" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="13" borderId="9" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="12" borderId="0" xfId="10" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="15" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="12" borderId="0" xfId="10" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="29" fillId="3" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="29" fillId="14" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="14" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="12" borderId="0" xfId="10" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -6436,7 +6414,7 @@
     <xf numFmtId="164" fontId="17" fillId="14" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="13" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6445,27 +6423,27 @@
     <xf numFmtId="164" fontId="16" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="33" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="10" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="34" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="32" fillId="5" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="31" fillId="5" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="33" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="1" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="34" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="33" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="28" fillId="6" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="27" fillId="6" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="22" fillId="6" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6483,14 +6461,14 @@
     <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="34" fillId="6" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="33" fillId="6" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="16" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="165" fontId="28" fillId="16" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="27" fillId="16" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="165" fontId="27" fillId="16" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="28" fillId="16" borderId="1" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="27" fillId="16" borderId="1" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="20" fillId="10" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6499,25 +6477,25 @@
     <xf numFmtId="165" fontId="24" fillId="12" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="37" fillId="6" borderId="1" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="36" fillId="6" borderId="1" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="24" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="28" fillId="3" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="27" fillId="3" borderId="1" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="168" fontId="19" fillId="6" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="38" fillId="3" borderId="1" xfId="16" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="164" fontId="37" fillId="3" borderId="1" xfId="16" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="9" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="38" fillId="9" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="40" fillId="9" borderId="1" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="39" fillId="9" borderId="1" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -6525,77 +6503,45 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="39" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="40" fillId="9" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="39" fillId="9" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="40" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="27" fillId="9" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="39" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="39" fillId="11" borderId="1" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="22" fillId="9" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="40" fillId="11" borderId="1" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="5" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="13" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="10" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="14" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="5" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="13" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="30" fillId="15" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="15" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="14" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="14" borderId="9" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6604,32 +6550,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="5" borderId="7" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="25" fillId="5" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
@@ -6639,13 +6568,50 @@
     <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="28" fillId="14" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="14" borderId="9" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="15" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="5" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="13" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="29" fillId="15" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="13" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="10" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="14" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="13" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="13" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="10" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6660,13 +6626,30 @@
     <xf numFmtId="164" fontId="17" fillId="12" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="5" borderId="7" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="35" fillId="5" borderId="7" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="39" fillId="9" borderId="1" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="171" fontId="39" fillId="11" borderId="1" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="8" xfId="10" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="8" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="170" fontId="39" fillId="0" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="10" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="170" fontId="39" fillId="0" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -8554,18 +8537,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
     </row>
     <row r="2" spans="1:1024" ht="24.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="139" t="s">
+      <c r="A2" s="121" t="s">
         <v>217</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
+      <c r="B2" s="121"/>
+      <c r="C2" s="121"/>
     </row>
     <row r="3" spans="1:1024" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -8585,7 +8568,7 @@
       <c r="B4" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="104" t="s">
         <v>223</v>
       </c>
     </row>
@@ -8596,7 +8579,7 @@
       <c r="B5" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C5" s="112" t="s">
+      <c r="C5" s="104" t="s">
         <v>224</v>
       </c>
     </row>
@@ -8607,7 +8590,7 @@
       <c r="B6" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C6" s="112" t="s">
+      <c r="C6" s="104" t="s">
         <v>225</v>
       </c>
     </row>
@@ -8618,7 +8601,7 @@
       <c r="B7" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C7" s="112" t="s">
+      <c r="C7" s="104" t="s">
         <v>226</v>
       </c>
     </row>
@@ -8629,7 +8612,7 @@
       <c r="B8" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C8" s="112" t="s">
+      <c r="C8" s="104" t="s">
         <v>227</v>
       </c>
     </row>
@@ -8717,38 +8700,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="F1" s="140" t="s">
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="F1" s="116" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
     </row>
     <row r="2" spans="1:1024" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="141" t="s">
+      <c r="A2" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="F2" s="142" t="s">
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="F2" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
-      <c r="K2" s="142"/>
-      <c r="L2" s="142"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
     </row>
     <row r="3" spans="1:1024" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -8769,20 +8752,20 @@
       <c r="G3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="143" t="s">
+      <c r="H3" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="143"/>
-      <c r="J3" s="143"/>
-      <c r="K3" s="143"/>
-      <c r="L3" s="143"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="L3" s="119"/>
     </row>
     <row r="4" spans="1:1024" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="144" t="s">
+      <c r="A4" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="144"/>
-      <c r="C4" s="144"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
       <c r="D4" s="8" t="s">
         <v>17</v>
       </c>
@@ -9025,11 +9008,11 @@
       </c>
     </row>
     <row r="11" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="144" t="s">
+      <c r="A11" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="144"/>
-      <c r="C11" s="144"/>
+      <c r="B11" s="113"/>
+      <c r="C11" s="113"/>
       <c r="D11" s="8">
         <f>SUM(D5:D10)</f>
         <v>48</v>
@@ -9142,8 +9125,8 @@
       <c r="B15" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="113" t="s">
-        <v>269</v>
+      <c r="C15" s="105" t="s">
+        <v>268</v>
       </c>
       <c r="D15" s="13">
         <v>7</v>
@@ -9163,7 +9146,7 @@
       <c r="B16" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="113" t="s">
+      <c r="C16" s="105" t="s">
         <v>34</v>
       </c>
       <c r="D16" s="13">
@@ -9258,11 +9241,11 @@
       <c r="L20" s="18"/>
     </row>
     <row r="21" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="144" t="s">
+      <c r="A21" s="113" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="144"/>
-      <c r="C21" s="144"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="113"/>
       <c r="D21" s="8">
         <f>SUM(D12:D20)</f>
         <v>65</v>
@@ -9299,8 +9282,8 @@
       <c r="B23" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="113" t="s">
-        <v>270</v>
+      <c r="C23" s="105" t="s">
+        <v>269</v>
       </c>
       <c r="D23" s="13">
         <v>5</v>
@@ -9313,8 +9296,8 @@
       <c r="B24" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="113" t="s">
-        <v>271</v>
+      <c r="C24" s="105" t="s">
+        <v>270</v>
       </c>
       <c r="D24" s="13">
         <v>10</v>
@@ -9327,8 +9310,8 @@
       <c r="B25" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="113" t="s">
-        <v>272</v>
+      <c r="C25" s="105" t="s">
+        <v>271</v>
       </c>
       <c r="D25" s="13">
         <v>5</v>
@@ -9341,7 +9324,7 @@
       <c r="B26" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="113" t="s">
+      <c r="C26" s="105" t="s">
         <v>228</v>
       </c>
       <c r="D26" s="13">
@@ -9355,8 +9338,8 @@
       <c r="B27" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="113" t="s">
-        <v>273</v>
+      <c r="C27" s="105" t="s">
+        <v>272</v>
       </c>
       <c r="D27" s="13">
         <v>5</v>
@@ -9369,7 +9352,7 @@
       <c r="B28" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="113" t="s">
+      <c r="C28" s="105" t="s">
         <v>229</v>
       </c>
       <c r="D28" s="13">
@@ -9383,7 +9366,7 @@
       <c r="B29" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="113" t="s">
+      <c r="C29" s="105" t="s">
         <v>230</v>
       </c>
       <c r="D29" s="13">
@@ -9397,8 +9380,8 @@
       <c r="B30" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="113" t="s">
-        <v>274</v>
+      <c r="C30" s="105" t="s">
+        <v>273</v>
       </c>
       <c r="D30" s="13">
         <v>10</v>
@@ -9411,7 +9394,7 @@
       <c r="B31" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="113" t="s">
+      <c r="C31" s="105" t="s">
         <v>231</v>
       </c>
       <c r="D31" s="13">
@@ -9425,7 +9408,7 @@
       <c r="B32" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="113" t="s">
+      <c r="C32" s="105" t="s">
         <v>232</v>
       </c>
       <c r="D32" s="13">
@@ -9439,7 +9422,7 @@
       <c r="B33" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="113" t="s">
+      <c r="C33" s="105" t="s">
         <v>233</v>
       </c>
       <c r="D33" s="13">
@@ -9453,7 +9436,7 @@
       <c r="B34" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="113" t="s">
+      <c r="C34" s="105" t="s">
         <v>234</v>
       </c>
       <c r="D34" s="13">
@@ -9467,7 +9450,7 @@
       <c r="B35" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="113" t="s">
+      <c r="C35" s="105" t="s">
         <v>235</v>
       </c>
       <c r="D35" s="13">
@@ -9481,7 +9464,7 @@
       <c r="B36" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="113" t="s">
+      <c r="C36" s="105" t="s">
         <v>236</v>
       </c>
       <c r="D36" s="13">
@@ -9517,11 +9500,11 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="144" t="s">
+      <c r="A39" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="144"/>
-      <c r="C39" s="144"/>
+      <c r="B39" s="113"/>
+      <c r="C39" s="113"/>
       <c r="D39" s="8">
         <f>SUM(D22:D38)</f>
         <v>120</v>
@@ -9654,9 +9637,9 @@
       </c>
     </row>
     <row r="49" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="145"/>
-      <c r="B49" s="145"/>
-      <c r="C49" s="145"/>
+      <c r="A49" s="114"/>
+      <c r="B49" s="114"/>
+      <c r="C49" s="114"/>
       <c r="D49" s="8">
         <f>SUM(D40:D48)</f>
         <v>82</v>
@@ -9670,16 +9653,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="F1:L1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="F2:L2"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:L1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="F2:L2"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="A4:C4"/>
   </mergeCells>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="1.1437007874015752" bottom="1.1437007874015752" header="0.75000000000000011" footer="0.75000000000000011"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -9702,19 +9685,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
     </row>
     <row r="2" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="148" t="s">
+      <c r="A3" s="123" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="148"/>
-      <c r="C3" s="148"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
     </row>
     <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
@@ -9823,11 +9806,11 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="148" t="s">
+      <c r="A14" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="148"/>
-      <c r="C14" s="148"/>
+      <c r="B14" s="123"/>
+      <c r="C14" s="123"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
@@ -9924,9 +9907,9 @@
   <dimension ref="A1:AMJ12"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.09765625" style="60" customWidth="1"/>
+    <col min="1" max="1" width="6.09765625" style="52" customWidth="1"/>
     <col min="2" max="2" width="45.19921875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.8984375" style="60" customWidth="1"/>
+    <col min="3" max="3" width="13.8984375" style="52" customWidth="1"/>
     <col min="4" max="6" width="13.09765625" style="4" customWidth="1"/>
     <col min="7" max="9" width="13" style="4" customWidth="1"/>
     <col min="10" max="10" width="13" style="20" customWidth="1"/>
@@ -9936,54 +9919,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="124" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
     </row>
     <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="125" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
       <c r="E2" s="41">
         <f>Planejamento!$B$10</f>
         <v>456.75</v>
       </c>
       <c r="F2" s="42"/>
-      <c r="G2" s="149" t="s">
+      <c r="G2" s="125" t="s">
         <v>75</v>
       </c>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="149"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
       <c r="K2" s="41"/>
     </row>
     <row r="3" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="43"/>
       <c r="B3" s="44"/>
-      <c r="C3" s="150" t="s">
+      <c r="C3" s="126" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="150"/>
-      <c r="E3" s="150"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
       <c r="F3" s="45"/>
-      <c r="G3" s="151" t="s">
+      <c r="G3" s="127" t="s">
         <v>77</v>
       </c>
-      <c r="H3" s="151"/>
-      <c r="I3" s="151"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
       <c r="J3" s="47"/>
       <c r="K3" s="48"/>
     </row>
@@ -10023,197 +10006,207 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="115">
+      <c r="A5" s="107">
         <v>1</v>
       </c>
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="117">
+      <c r="C5" s="109">
         <v>46252</v>
       </c>
-      <c r="D5" s="117">
+      <c r="D5" s="109">
         <v>46262</v>
       </c>
-      <c r="E5" s="114">
+      <c r="E5" s="106">
         <v>60</v>
       </c>
-      <c r="F5" s="118" t="s">
+      <c r="F5" s="110" t="s">
         <v>87</v>
       </c>
-      <c r="G5" s="117">
+      <c r="G5" s="109">
         <v>46252</v>
       </c>
-      <c r="H5" s="117">
+      <c r="H5" s="109">
         <v>46262</v>
       </c>
-      <c r="I5" s="114">
+      <c r="I5" s="106">
         <v>50</v>
       </c>
-      <c r="J5" s="123">
+      <c r="J5" s="112">
         <f>E5-I5</f>
         <v>10</v>
       </c>
-      <c r="K5" s="120" t="s">
+      <c r="K5" s="111" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="107">
+        <v>2</v>
+      </c>
+      <c r="B6" s="108" t="s">
+        <v>274</v>
+      </c>
+      <c r="C6" s="109">
+        <v>46279</v>
+      </c>
+      <c r="D6" s="109">
+        <v>46290</v>
+      </c>
+      <c r="E6" s="106">
+        <v>85</v>
+      </c>
+      <c r="F6" s="110" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="109">
+        <v>46280</v>
+      </c>
+      <c r="H6" s="109">
+        <v>46296</v>
+      </c>
+      <c r="I6" s="151">
+        <v>95</v>
+      </c>
+      <c r="J6" s="152">
+        <v>5</v>
+      </c>
+      <c r="K6" s="111" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="115">
-        <v>2</v>
-      </c>
-      <c r="B6" s="116" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="107">
+        <v>3</v>
+      </c>
+      <c r="B7" s="108" t="s">
         <v>245</v>
       </c>
-      <c r="C6" s="117">
-        <v>46265</v>
-      </c>
-      <c r="D6" s="117">
-        <v>46276</v>
-      </c>
-      <c r="E6" s="114">
+      <c r="C7" s="109">
+        <v>46293</v>
+      </c>
+      <c r="D7" s="109">
+        <v>46304</v>
+      </c>
+      <c r="E7" s="106">
         <v>76</v>
       </c>
-      <c r="F6" s="118" t="s">
+      <c r="F7" s="110" t="s">
+        <v>275</v>
+      </c>
+      <c r="G7" s="109">
+        <v>46297</v>
+      </c>
+      <c r="H7" s="109"/>
+      <c r="I7" s="151"/>
+      <c r="J7" s="152"/>
+      <c r="K7" s="111" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="107">
+        <v>4</v>
+      </c>
+      <c r="B8" s="108" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="109">
+        <v>46307</v>
+      </c>
+      <c r="D8" s="109">
+        <v>46318</v>
+      </c>
+      <c r="E8" s="106">
+        <v>82</v>
+      </c>
+      <c r="F8" s="110" t="s">
         <v>88</v>
       </c>
-      <c r="G6" s="119"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="120" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="115">
-        <v>3</v>
-      </c>
-      <c r="B7" s="116" t="s">
-        <v>246</v>
-      </c>
-      <c r="C7" s="117">
-        <v>46279</v>
-      </c>
-      <c r="D7" s="117">
-        <v>46290</v>
-      </c>
-      <c r="E7" s="114">
-        <v>85</v>
-      </c>
-      <c r="F7" s="118" t="s">
+      <c r="G8" s="109"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="151"/>
+      <c r="J8" s="152"/>
+      <c r="K8" s="111" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="107">
+        <v>5</v>
+      </c>
+      <c r="B9" s="108" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="109">
+        <v>46321</v>
+      </c>
+      <c r="D9" s="109">
+        <v>46332</v>
+      </c>
+      <c r="E9" s="106">
+        <v>77</v>
+      </c>
+      <c r="F9" s="110" t="s">
         <v>88</v>
       </c>
-      <c r="G7" s="119"/>
-      <c r="H7" s="119"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="120" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A8" s="115">
-        <v>4</v>
-      </c>
-      <c r="B8" s="116" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" s="121">
-        <v>46293</v>
-      </c>
-      <c r="D8" s="121">
-        <v>46304</v>
-      </c>
-      <c r="E8" s="114">
-        <v>82</v>
-      </c>
-      <c r="F8" s="118" t="s">
+      <c r="G9" s="109"/>
+      <c r="H9" s="109"/>
+      <c r="I9" s="151"/>
+      <c r="J9" s="152"/>
+      <c r="K9" s="111" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A10" s="107">
+        <v>6</v>
+      </c>
+      <c r="B10" s="108" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="109">
+        <v>46335</v>
+      </c>
+      <c r="D10" s="109">
+        <v>46346</v>
+      </c>
+      <c r="E10" s="106">
+        <v>76.5</v>
+      </c>
+      <c r="F10" s="110" t="s">
         <v>88</v>
       </c>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="120" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="115">
-        <v>5</v>
-      </c>
-      <c r="B9" s="116" t="s">
-        <v>248</v>
-      </c>
-      <c r="C9" s="121">
-        <v>46307</v>
-      </c>
-      <c r="D9" s="121">
-        <v>46318</v>
-      </c>
-      <c r="E9" s="114">
-        <v>77</v>
-      </c>
-      <c r="F9" s="118" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="120" t="s">
+      <c r="G10" s="109"/>
+      <c r="H10" s="109"/>
+      <c r="I10" s="151"/>
+      <c r="J10" s="152"/>
+      <c r="K10" s="111" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A10" s="115">
-        <v>6</v>
-      </c>
-      <c r="B10" s="116" t="s">
-        <v>249</v>
-      </c>
-      <c r="C10" s="121">
-        <v>46321</v>
-      </c>
-      <c r="D10" s="121">
-        <v>46332</v>
-      </c>
-      <c r="E10" s="114">
-        <v>76.5</v>
-      </c>
-      <c r="F10" s="118" t="s">
-        <v>88</v>
-      </c>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="122" t="s">
-        <v>255</v>
-      </c>
-    </row>
     <row r="11" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="54"/>
-      <c r="B11" s="55"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="57">
+      <c r="A11" s="50"/>
+      <c r="B11" s="153"/>
+      <c r="C11" s="154"/>
+      <c r="D11" s="153"/>
+      <c r="E11" s="155">
         <f>SUM(E5:E10)</f>
         <v>456.5</v>
       </c>
-      <c r="F11" s="55"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="57">
+      <c r="F11" s="153"/>
+      <c r="G11" s="156"/>
+      <c r="H11" s="156"/>
+      <c r="I11" s="155">
         <f>SUM(I5:I10)</f>
-        <v>50</v>
-      </c>
-      <c r="J11" s="59">
+        <v>145</v>
+      </c>
+      <c r="J11" s="157">
         <f>SUM(J5:J10)</f>
-        <v>10</v>
-      </c>
-      <c r="K11" s="58"/>
+        <v>15</v>
+      </c>
+      <c r="K11" s="156"/>
     </row>
     <row r="12" spans="1:11" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="J12" s="20"/>
@@ -10226,7 +10219,7 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <phoneticPr fontId="42" type="noConversion"/>
+  <phoneticPr fontId="41" type="noConversion"/>
   <conditionalFormatting sqref="A5:D10 G5:H10">
     <cfRule type="expression" dxfId="7" priority="6" stopIfTrue="1">
       <formula>OR($F5="Planned",$F5="Unplanned")</formula>
@@ -10262,564 +10255,565 @@
   <dimension ref="A1:AMJ53"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.59765625" style="62" customWidth="1"/>
-    <col min="2" max="2" width="35.59765625" style="62" customWidth="1"/>
-    <col min="3" max="3" width="6.5" style="62" customWidth="1"/>
-    <col min="4" max="4" width="13.19921875" style="62" customWidth="1"/>
-    <col min="5" max="5" width="8.8984375" style="62" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="62" customWidth="1"/>
-    <col min="7" max="7" width="9.09765625" style="62" customWidth="1"/>
-    <col min="8" max="9" width="12.19921875" style="62" customWidth="1"/>
-    <col min="10" max="10" width="24.19921875" style="62" customWidth="1"/>
-    <col min="11" max="11" width="27.8984375" style="62" customWidth="1"/>
-    <col min="12" max="12" width="8.5" style="62" customWidth="1"/>
-    <col min="13" max="14" width="20.5" style="62" customWidth="1"/>
-    <col min="15" max="256" width="8.5" style="62" customWidth="1"/>
-    <col min="257" max="258" width="6.5" style="62" customWidth="1"/>
-    <col min="259" max="259" width="13.8984375" style="62" customWidth="1"/>
-    <col min="260" max="260" width="9" style="62" customWidth="1"/>
-    <col min="261" max="261" width="13.5" style="62" customWidth="1"/>
-    <col min="262" max="262" width="10" style="62" customWidth="1"/>
-    <col min="263" max="263" width="12.19921875" style="62" customWidth="1"/>
-    <col min="264" max="264" width="5.8984375" style="62" customWidth="1"/>
-    <col min="265" max="265" width="24.19921875" style="62" customWidth="1"/>
-    <col min="266" max="266" width="32.5" style="62" customWidth="1"/>
-    <col min="267" max="267" width="17.59765625" style="62" customWidth="1"/>
-    <col min="268" max="268" width="8.5" style="62" customWidth="1"/>
-    <col min="269" max="270" width="20.5" style="62" customWidth="1"/>
-    <col min="271" max="512" width="8.5" style="62" customWidth="1"/>
-    <col min="513" max="514" width="6.5" style="62" customWidth="1"/>
-    <col min="515" max="515" width="13.8984375" style="62" customWidth="1"/>
-    <col min="516" max="516" width="9" style="62" customWidth="1"/>
-    <col min="517" max="517" width="13.5" style="62" customWidth="1"/>
-    <col min="518" max="518" width="10" style="62" customWidth="1"/>
-    <col min="519" max="519" width="12.19921875" style="62" customWidth="1"/>
-    <col min="520" max="520" width="5.8984375" style="62" customWidth="1"/>
-    <col min="521" max="521" width="24.19921875" style="62" customWidth="1"/>
-    <col min="522" max="522" width="32.5" style="62" customWidth="1"/>
-    <col min="523" max="523" width="17.59765625" style="62" customWidth="1"/>
-    <col min="524" max="524" width="8.5" style="62" customWidth="1"/>
-    <col min="525" max="526" width="20.5" style="62" customWidth="1"/>
-    <col min="527" max="768" width="8.5" style="62" customWidth="1"/>
-    <col min="769" max="770" width="6.5" style="62" customWidth="1"/>
-    <col min="771" max="771" width="13.8984375" style="62" customWidth="1"/>
-    <col min="772" max="772" width="9" style="62" customWidth="1"/>
-    <col min="773" max="773" width="13.5" style="62" customWidth="1"/>
-    <col min="774" max="774" width="10" style="62" customWidth="1"/>
-    <col min="775" max="775" width="12.19921875" style="62" customWidth="1"/>
-    <col min="776" max="776" width="5.8984375" style="62" customWidth="1"/>
-    <col min="777" max="777" width="24.19921875" style="62" customWidth="1"/>
-    <col min="778" max="778" width="32.5" style="62" customWidth="1"/>
-    <col min="779" max="779" width="17.59765625" style="62" customWidth="1"/>
-    <col min="780" max="780" width="8.5" style="62" customWidth="1"/>
-    <col min="781" max="782" width="20.5" style="62" customWidth="1"/>
-    <col min="783" max="1024" width="8.5" style="62" customWidth="1"/>
+    <col min="1" max="1" width="5.59765625" style="54" customWidth="1"/>
+    <col min="2" max="2" width="35.59765625" style="54" customWidth="1"/>
+    <col min="3" max="3" width="6.5" style="54" customWidth="1"/>
+    <col min="4" max="4" width="13.19921875" style="54" customWidth="1"/>
+    <col min="5" max="5" width="8.8984375" style="54" customWidth="1"/>
+    <col min="6" max="6" width="12.5" style="54" customWidth="1"/>
+    <col min="7" max="7" width="9.09765625" style="54" customWidth="1"/>
+    <col min="8" max="9" width="12.19921875" style="54" customWidth="1"/>
+    <col min="10" max="10" width="24.19921875" style="54" customWidth="1"/>
+    <col min="11" max="11" width="27.8984375" style="54" customWidth="1"/>
+    <col min="12" max="12" width="8.5" style="54" customWidth="1"/>
+    <col min="13" max="14" width="20.5" style="54" customWidth="1"/>
+    <col min="15" max="256" width="8.5" style="54" customWidth="1"/>
+    <col min="257" max="258" width="6.5" style="54" customWidth="1"/>
+    <col min="259" max="259" width="13.8984375" style="54" customWidth="1"/>
+    <col min="260" max="260" width="9" style="54" customWidth="1"/>
+    <col min="261" max="261" width="13.5" style="54" customWidth="1"/>
+    <col min="262" max="262" width="10" style="54" customWidth="1"/>
+    <col min="263" max="263" width="12.19921875" style="54" customWidth="1"/>
+    <col min="264" max="264" width="5.8984375" style="54" customWidth="1"/>
+    <col min="265" max="265" width="24.19921875" style="54" customWidth="1"/>
+    <col min="266" max="266" width="32.5" style="54" customWidth="1"/>
+    <col min="267" max="267" width="17.59765625" style="54" customWidth="1"/>
+    <col min="268" max="268" width="8.5" style="54" customWidth="1"/>
+    <col min="269" max="270" width="20.5" style="54" customWidth="1"/>
+    <col min="271" max="512" width="8.5" style="54" customWidth="1"/>
+    <col min="513" max="514" width="6.5" style="54" customWidth="1"/>
+    <col min="515" max="515" width="13.8984375" style="54" customWidth="1"/>
+    <col min="516" max="516" width="9" style="54" customWidth="1"/>
+    <col min="517" max="517" width="13.5" style="54" customWidth="1"/>
+    <col min="518" max="518" width="10" style="54" customWidth="1"/>
+    <col min="519" max="519" width="12.19921875" style="54" customWidth="1"/>
+    <col min="520" max="520" width="5.8984375" style="54" customWidth="1"/>
+    <col min="521" max="521" width="24.19921875" style="54" customWidth="1"/>
+    <col min="522" max="522" width="32.5" style="54" customWidth="1"/>
+    <col min="523" max="523" width="17.59765625" style="54" customWidth="1"/>
+    <col min="524" max="524" width="8.5" style="54" customWidth="1"/>
+    <col min="525" max="526" width="20.5" style="54" customWidth="1"/>
+    <col min="527" max="768" width="8.5" style="54" customWidth="1"/>
+    <col min="769" max="770" width="6.5" style="54" customWidth="1"/>
+    <col min="771" max="771" width="13.8984375" style="54" customWidth="1"/>
+    <col min="772" max="772" width="9" style="54" customWidth="1"/>
+    <col min="773" max="773" width="13.5" style="54" customWidth="1"/>
+    <col min="774" max="774" width="10" style="54" customWidth="1"/>
+    <col min="775" max="775" width="12.19921875" style="54" customWidth="1"/>
+    <col min="776" max="776" width="5.8984375" style="54" customWidth="1"/>
+    <col min="777" max="777" width="24.19921875" style="54" customWidth="1"/>
+    <col min="778" max="778" width="32.5" style="54" customWidth="1"/>
+    <col min="779" max="779" width="17.59765625" style="54" customWidth="1"/>
+    <col min="780" max="780" width="8.5" style="54" customWidth="1"/>
+    <col min="781" max="782" width="20.5" style="54" customWidth="1"/>
+    <col min="783" max="1024" width="8.5" style="54" customWidth="1"/>
     <col min="1025" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="61" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="125" t="s">
+    <row r="1" spans="1:11" s="53" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="124" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
     </row>
     <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="63" t="s">
+      <c r="D3" s="55" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="64" t="s">
+      <c r="D4" s="56" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="56" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D6" s="64" t="s">
+      <c r="D6" s="56" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="64" t="s">
+      <c r="D7" s="56" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D8" s="64" t="s">
+      <c r="D8" s="56" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D9" s="64" t="s">
+      <c r="D9" s="56" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D10" s="64" t="s">
+      <c r="D10" s="56" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="64" t="s">
+      <c r="D11" s="56" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="64" t="s">
+      <c r="D12" s="56" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D13" s="64" t="s">
+      <c r="D13" s="56" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="63" t="s">
+      <c r="D14" s="55" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="64" t="s">
+      <c r="D15" s="56" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="64" t="s">
+      <c r="D16" s="56" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="17" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D17" s="64" t="s">
+      <c r="D17" s="56" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="18" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="63" t="s">
+      <c r="D18" s="55" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="19" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="64" t="s">
+      <c r="D19" s="56" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="20" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="64" t="s">
+      <c r="D20" s="56" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="21" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="64" t="s">
+      <c r="D21" s="56" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="22" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="63" t="s">
+      <c r="D22" s="55" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="23" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="64" t="s">
+      <c r="D23" s="56" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="24" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="64" t="s">
+      <c r="D24" s="56" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="25" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="64" t="s">
+      <c r="D25" s="56" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="26" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="64" t="s">
+      <c r="D26" s="56" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="27" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D27" s="63" t="s">
+      <c r="D27" s="55" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="28" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="64" t="s">
+      <c r="D28" s="56" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="29" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="64" t="s">
+      <c r="D29" s="56" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="30" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="64" t="s">
+      <c r="D30" s="56" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="4:4" s="65" customFormat="1" ht="10.199999999999999" hidden="1" x14ac:dyDescent="0.2">
-      <c r="D31" s="66" t="s">
+    <row r="31" spans="4:4" s="57" customFormat="1" ht="10.199999999999999" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D31" s="58" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="32" spans="4:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="67" t="s">
+      <c r="D32" s="59" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="126" t="s">
+      <c r="D33" s="137" t="s">
         <v>120</v>
       </c>
-      <c r="E33" s="126"/>
+      <c r="E33" s="137"/>
     </row>
     <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D34" s="64">
+      <c r="D34" s="56">
         <v>4290</v>
       </c>
-      <c r="E34" s="64" t="s">
+      <c r="E34" s="56" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D35" s="64">
+      <c r="D35" s="56">
         <v>5082</v>
       </c>
-      <c r="E35" s="64" t="s">
+      <c r="E35" s="56" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D36" s="64">
+      <c r="D36" s="56">
         <v>4356</v>
       </c>
-      <c r="E36" s="64" t="s">
+      <c r="E36" s="56" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="64">
+      <c r="D37" s="56">
         <v>5929</v>
       </c>
-      <c r="E37" s="64" t="s">
+      <c r="E37" s="56" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="64">
+      <c r="D38" s="56">
         <v>5005</v>
       </c>
-      <c r="E38" s="64" t="s">
+      <c r="E38" s="56" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="64">
+      <c r="D39" s="56">
         <v>4225</v>
       </c>
-      <c r="E39" s="64" t="s">
+      <c r="E39" s="56" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:11" s="61" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="127" t="s">
+    <row r="41" spans="1:11" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="138" t="s">
         <v>127</v>
       </c>
-      <c r="B41" s="127"/>
-      <c r="C41" s="127"/>
-      <c r="D41" s="127"/>
-      <c r="E41" s="127"/>
-      <c r="F41" s="127"/>
-      <c r="G41" s="127"/>
-      <c r="H41" s="127"/>
-      <c r="I41" s="127"/>
-      <c r="J41" s="127"/>
-      <c r="K41" s="127"/>
-    </row>
-    <row r="42" spans="1:11" s="61" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="128" t="s">
+      <c r="B41" s="138"/>
+      <c r="C41" s="138"/>
+      <c r="D41" s="138"/>
+      <c r="E41" s="138"/>
+      <c r="F41" s="138"/>
+      <c r="G41" s="138"/>
+      <c r="H41" s="138"/>
+      <c r="I41" s="138"/>
+      <c r="J41" s="138"/>
+      <c r="K41" s="138"/>
+    </row>
+    <row r="42" spans="1:11" s="53" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="139" t="s">
         <v>128</v>
       </c>
-      <c r="B42" s="128"/>
-      <c r="C42" s="128"/>
-      <c r="D42" s="128"/>
-      <c r="E42" s="128"/>
-      <c r="F42" s="128"/>
-      <c r="G42" s="128"/>
-      <c r="H42" s="128"/>
-      <c r="I42" s="128"/>
-      <c r="J42" s="128"/>
-      <c r="K42" s="128"/>
-    </row>
-    <row r="43" spans="1:11" s="61" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="129" t="s">
+      <c r="B42" s="139"/>
+      <c r="C42" s="139"/>
+      <c r="D42" s="139"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="139"/>
+      <c r="H42" s="139"/>
+      <c r="I42" s="139"/>
+      <c r="J42" s="139"/>
+      <c r="K42" s="139"/>
+    </row>
+    <row r="43" spans="1:11" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="140" t="s">
         <v>129</v>
       </c>
-      <c r="B43" s="129"/>
-      <c r="C43" s="129"/>
-      <c r="D43" s="129"/>
-      <c r="E43" s="129"/>
-      <c r="F43" s="129"/>
-      <c r="G43" s="129"/>
-      <c r="H43" s="129"/>
-      <c r="I43" s="129"/>
-      <c r="J43" s="129"/>
-      <c r="K43" s="129"/>
-    </row>
-    <row r="44" spans="1:11" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="124" t="s">
+      <c r="B43" s="140"/>
+      <c r="C43" s="140"/>
+      <c r="D43" s="140"/>
+      <c r="E43" s="140"/>
+      <c r="F43" s="140"/>
+      <c r="G43" s="140"/>
+      <c r="H43" s="140"/>
+      <c r="I43" s="140"/>
+      <c r="J43" s="140"/>
+      <c r="K43" s="140"/>
+    </row>
+    <row r="44" spans="1:11" s="53" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="136" t="s">
         <v>130</v>
       </c>
-      <c r="B44" s="124"/>
-      <c r="C44" s="124"/>
-      <c r="D44" s="124"/>
-      <c r="E44" s="124"/>
-      <c r="F44" s="124"/>
-      <c r="G44" s="124"/>
-      <c r="H44" s="124"/>
-      <c r="I44" s="124"/>
-      <c r="J44" s="124"/>
-      <c r="K44" s="124"/>
+      <c r="B44" s="136"/>
+      <c r="C44" s="136"/>
+      <c r="D44" s="136"/>
+      <c r="E44" s="136"/>
+      <c r="F44" s="136"/>
+      <c r="G44" s="136"/>
+      <c r="H44" s="136"/>
+      <c r="I44" s="136"/>
+      <c r="J44" s="136"/>
+      <c r="K44" s="136"/>
     </row>
     <row r="45" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="130" t="s">
+      <c r="A46" s="132" t="s">
         <v>131</v>
       </c>
-      <c r="B46" s="130"/>
-      <c r="C46" s="130"/>
-      <c r="D46" s="130"/>
-      <c r="E46" s="130"/>
-      <c r="F46" s="130"/>
-      <c r="G46" s="130"/>
-      <c r="H46" s="130"/>
-      <c r="I46" s="130"/>
-      <c r="J46" s="130"/>
-      <c r="K46" s="130"/>
-    </row>
-    <row r="47" spans="1:11" s="70" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="68" t="s">
+      <c r="B46" s="132"/>
+      <c r="C46" s="132"/>
+      <c r="D46" s="132"/>
+      <c r="E46" s="132"/>
+      <c r="F46" s="132"/>
+      <c r="G46" s="132"/>
+      <c r="H46" s="132"/>
+      <c r="I46" s="132"/>
+      <c r="J46" s="132"/>
+      <c r="K46" s="132"/>
+    </row>
+    <row r="47" spans="1:11" s="62" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="B47" s="69"/>
-      <c r="C47" s="131" t="s">
+      <c r="B47" s="61"/>
+      <c r="C47" s="133" t="s">
         <v>133</v>
       </c>
-      <c r="D47" s="131"/>
-      <c r="E47" s="131"/>
-      <c r="F47" s="131"/>
-      <c r="G47" s="131"/>
-      <c r="H47" s="131"/>
-      <c r="I47" s="131"/>
-      <c r="J47" s="131"/>
-      <c r="K47" s="131"/>
-    </row>
-    <row r="48" spans="1:11" s="72" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="132"/>
-      <c r="B48" s="133" t="s">
+      <c r="D47" s="133"/>
+      <c r="E47" s="133"/>
+      <c r="F47" s="133"/>
+      <c r="G47" s="133"/>
+      <c r="H47" s="133"/>
+      <c r="I47" s="133"/>
+      <c r="J47" s="133"/>
+      <c r="K47" s="133"/>
+    </row>
+    <row r="48" spans="1:11" s="64" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="134"/>
+      <c r="B48" s="130" t="s">
         <v>134</v>
       </c>
-      <c r="C48" s="133" t="s">
+      <c r="C48" s="130" t="s">
         <v>135</v>
       </c>
-      <c r="D48" s="133" t="s">
+      <c r="D48" s="130" t="s">
         <v>136</v>
       </c>
-      <c r="E48" s="133" t="s">
+      <c r="E48" s="130" t="s">
         <v>105</v>
       </c>
-      <c r="F48" s="133" t="s">
+      <c r="F48" s="130" t="s">
         <v>137</v>
       </c>
-      <c r="G48" s="133" t="s">
+      <c r="G48" s="130" t="s">
         <v>109</v>
       </c>
-      <c r="H48" s="134" t="s">
+      <c r="H48" s="135" t="s">
         <v>138</v>
       </c>
-      <c r="I48" s="134"/>
-      <c r="J48" s="134"/>
-      <c r="K48" s="134"/>
-    </row>
-    <row r="49" spans="1:11" s="72" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="132"/>
-      <c r="B49" s="133"/>
-      <c r="C49" s="133"/>
-      <c r="D49" s="133"/>
-      <c r="E49" s="133"/>
-      <c r="F49" s="133"/>
-      <c r="G49" s="133"/>
-      <c r="H49" s="133" t="s">
+      <c r="I48" s="135"/>
+      <c r="J48" s="135"/>
+      <c r="K48" s="135"/>
+    </row>
+    <row r="49" spans="1:11" s="64" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="134"/>
+      <c r="B49" s="130"/>
+      <c r="C49" s="130"/>
+      <c r="D49" s="130"/>
+      <c r="E49" s="130"/>
+      <c r="F49" s="130"/>
+      <c r="G49" s="130"/>
+      <c r="H49" s="130" t="s">
         <v>139</v>
       </c>
-      <c r="I49" s="133"/>
-      <c r="J49" s="71" t="s">
+      <c r="I49" s="130"/>
+      <c r="J49" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="K49" s="71" t="s">
+      <c r="K49" s="63" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="50" spans="1:11" s="72" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A50" s="73">
+    <row r="50" spans="1:11" s="64" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A50" s="65">
         <v>1</v>
       </c>
-      <c r="B50" s="73" t="s">
+      <c r="B50" s="65" t="s">
         <v>142</v>
       </c>
-      <c r="C50" s="74">
+      <c r="C50" s="66">
         <v>46252</v>
       </c>
-      <c r="D50" s="75" t="s">
+      <c r="D50" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="75" t="s">
+      <c r="E50" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="F50" s="76" t="str">
+      <c r="F50" s="68" t="str">
         <f t="shared" ref="F50:F53" si="0">IF(OR((CODE($D50)*CODE($E50))=$D$36,(CODE($D50)*CODE($E50))=$D$35),$D$15,IF(OR((CODE($D50)*CODE($E50))=$D$34,(CODE($D50)*CODE($E50))=$D$37),$D$16,IF(OR((CODE($D50)*CODE($E50))=$D$38,(CODE($D50)*CODE($E50))=$D$39),$D$17,0)))</f>
         <v>Alta</v>
       </c>
-      <c r="G50" s="75" t="s">
+      <c r="G50" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="H50" s="137" t="s">
+      <c r="H50" s="131" t="s">
+        <v>256</v>
+      </c>
+      <c r="I50" s="131"/>
+      <c r="J50" s="67" t="s">
+        <v>255</v>
+      </c>
+      <c r="K50" s="67" t="s">
         <v>257</v>
       </c>
-      <c r="I50" s="137"/>
-      <c r="J50" s="75" t="s">
-        <v>256</v>
-      </c>
-      <c r="K50" s="75" t="s">
+    </row>
+    <row r="51" spans="1:11" s="64" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A51" s="65">
+        <v>2</v>
+      </c>
+      <c r="B51" s="65" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" s="72" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A51" s="73">
-        <v>2</v>
-      </c>
-      <c r="B51" s="73" t="s">
-        <v>259</v>
-      </c>
-      <c r="C51" s="74">
+      <c r="C51" s="66">
         <v>46252</v>
       </c>
-      <c r="D51" s="75" t="s">
+      <c r="D51" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="E51" s="75" t="s">
+      <c r="E51" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="F51" s="76" t="str">
+      <c r="F51" s="68" t="str">
         <f t="shared" si="0"/>
         <v>Média</v>
       </c>
-      <c r="G51" s="75" t="s">
+      <c r="G51" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="H51" s="135" t="s">
-        <v>257</v>
-      </c>
-      <c r="I51" s="136"/>
-      <c r="J51" s="75" t="s">
+      <c r="H51" s="128" t="s">
+        <v>256</v>
+      </c>
+      <c r="I51" s="129"/>
+      <c r="J51" s="67" t="s">
+        <v>259</v>
+      </c>
+      <c r="K51" s="67" t="s">
         <v>260</v>
       </c>
-      <c r="K51" s="75" t="s">
+    </row>
+    <row r="52" spans="1:11" s="64" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A52" s="65">
+        <v>3</v>
+      </c>
+      <c r="B52" s="65" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" s="72" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A52" s="73">
-        <v>3</v>
-      </c>
-      <c r="B52" s="73" t="s">
-        <v>262</v>
-      </c>
-      <c r="C52" s="74">
+      <c r="C52" s="66">
         <v>46252</v>
       </c>
-      <c r="D52" s="75" t="s">
+      <c r="D52" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="E52" s="75" t="s">
+      <c r="E52" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="F52" s="76" t="str">
+      <c r="F52" s="68" t="str">
         <f t="shared" si="0"/>
         <v>Alta</v>
       </c>
-      <c r="G52" s="75" t="s">
+      <c r="G52" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="H52" s="135" t="s">
-        <v>257</v>
-      </c>
-      <c r="I52" s="136"/>
-      <c r="J52" s="75" t="s">
+      <c r="H52" s="128" t="s">
+        <v>256</v>
+      </c>
+      <c r="I52" s="129"/>
+      <c r="J52" s="67" t="s">
+        <v>262</v>
+      </c>
+      <c r="K52" s="67" t="s">
         <v>263</v>
       </c>
-      <c r="K52" s="75" t="s">
+    </row>
+    <row r="53" spans="1:11" s="64" customFormat="1" ht="30.6" x14ac:dyDescent="0.25">
+      <c r="A53" s="65">
+        <v>4</v>
+      </c>
+      <c r="B53" s="65" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" s="72" customFormat="1" ht="30.6" x14ac:dyDescent="0.25">
-      <c r="A53" s="73">
-        <v>4</v>
-      </c>
-      <c r="B53" s="73" t="s">
-        <v>265</v>
-      </c>
-      <c r="C53" s="74">
+      <c r="C53" s="66">
         <v>46252</v>
       </c>
-      <c r="D53" s="75" t="s">
+      <c r="D53" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="E53" s="75" t="s">
+      <c r="E53" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="F53" s="76" t="str">
+      <c r="F53" s="68" t="str">
         <f t="shared" si="0"/>
         <v>Baixa</v>
       </c>
-      <c r="G53" s="75" t="s">
+      <c r="G53" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="H53" s="135" t="s">
+      <c r="H53" s="128" t="s">
+        <v>265</v>
+      </c>
+      <c r="I53" s="129"/>
+      <c r="J53" s="67" t="s">
         <v>266</v>
       </c>
-      <c r="I53" s="136"/>
-      <c r="J53" s="75" t="s">
+      <c r="K53" s="67" t="s">
         <v>267</v>
-      </c>
-      <c r="K53" s="75" t="s">
-        <v>268</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A43:K43"/>
     <mergeCell ref="A46:K46"/>
     <mergeCell ref="C47:K47"/>
     <mergeCell ref="A48:A49"/>
@@ -10830,12 +10824,11 @@
     <mergeCell ref="F48:F49"/>
     <mergeCell ref="G48:G49"/>
     <mergeCell ref="H48:K48"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H52:I52"/>
   </mergeCells>
   <conditionalFormatting sqref="F50:F53">
     <cfRule type="cellIs" dxfId="2" priority="8" stopIfTrue="1" operator="equal">
@@ -10892,432 +10885,432 @@
     <col min="1025" max="1025" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="61" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="154" t="s">
+    <row r="1" spans="1:23" s="53" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="143" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
-      <c r="L1" s="154"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="154"/>
-    </row>
-    <row r="2" spans="1:23" s="77" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="155" t="s">
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="143"/>
+      <c r="L1" s="143"/>
+      <c r="M1" s="143"/>
+      <c r="N1" s="143"/>
+    </row>
+    <row r="2" spans="1:23" s="69" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="155"/>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
-      <c r="L2" s="155"/>
-      <c r="M2" s="155"/>
-      <c r="N2" s="155"/>
-    </row>
-    <row r="3" spans="1:23" s="77" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="156" t="s">
+      <c r="B2" s="144"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
+      <c r="L2" s="144"/>
+      <c r="M2" s="144"/>
+      <c r="N2" s="144"/>
+    </row>
+    <row r="3" spans="1:23" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="145" t="s">
         <v>144</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156"/>
-      <c r="K3" s="156"/>
-      <c r="L3" s="156"/>
-      <c r="M3" s="156"/>
-      <c r="N3" s="156"/>
-    </row>
-    <row r="4" spans="1:23" s="77" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="157" t="s">
+      <c r="B3" s="145"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="145"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="145"/>
+      <c r="H3" s="145"/>
+      <c r="I3" s="145"/>
+      <c r="J3" s="145"/>
+      <c r="K3" s="145"/>
+      <c r="L3" s="145"/>
+      <c r="M3" s="145"/>
+      <c r="N3" s="145"/>
+    </row>
+    <row r="4" spans="1:23" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="146" t="s">
         <v>145</v>
       </c>
-      <c r="B4" s="157"/>
-      <c r="C4" s="157"/>
-      <c r="D4" s="157"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="157"/>
-      <c r="G4" s="157"/>
-      <c r="H4" s="157"/>
-      <c r="I4" s="157"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="157"/>
-      <c r="L4" s="157"/>
-      <c r="M4" s="157"/>
-      <c r="N4" s="157"/>
-    </row>
-    <row r="5" spans="1:23" s="77" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="158" t="s">
+      <c r="B4" s="146"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
+      <c r="N4" s="146"/>
+    </row>
+    <row r="5" spans="1:23" s="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="147" t="s">
         <v>146</v>
       </c>
-      <c r="B5" s="158"/>
-      <c r="C5" s="158"/>
-      <c r="D5" s="158"/>
-      <c r="E5" s="158"/>
-      <c r="F5" s="158"/>
-      <c r="G5" s="158"/>
-      <c r="H5" s="158"/>
-      <c r="I5" s="158"/>
-      <c r="J5" s="158"/>
-      <c r="K5" s="158"/>
-      <c r="L5" s="158"/>
-      <c r="M5" s="158"/>
-      <c r="N5" s="158"/>
+      <c r="B5" s="147"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="147"/>
+      <c r="E5" s="147"/>
+      <c r="F5" s="147"/>
+      <c r="G5" s="147"/>
+      <c r="H5" s="147"/>
+      <c r="I5" s="147"/>
+      <c r="J5" s="147"/>
+      <c r="K5" s="147"/>
+      <c r="L5" s="147"/>
+      <c r="M5" s="147"/>
+      <c r="N5" s="147"/>
     </row>
     <row r="6" spans="1:23" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:23" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="152" t="s">
+      <c r="A7" s="141" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="152"/>
-      <c r="D7" s="152" t="s">
+      <c r="B7" s="141"/>
+      <c r="D7" s="141" t="s">
         <v>148</v>
       </c>
-      <c r="E7" s="152"/>
-      <c r="G7" s="152" t="s">
+      <c r="E7" s="141"/>
+      <c r="G7" s="141" t="s">
         <v>149</v>
       </c>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="152"/>
-      <c r="M7" s="152" t="s">
+      <c r="H7" s="141"/>
+      <c r="I7" s="141"/>
+      <c r="J7" s="141"/>
+      <c r="K7" s="141"/>
+      <c r="M7" s="141" t="s">
         <v>150</v>
       </c>
-      <c r="N7" s="152"/>
+      <c r="N7" s="141"/>
     </row>
     <row r="8" spans="1:23" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="72" t="s">
         <v>151</v>
       </c>
-      <c r="B8" s="81" t="s">
+      <c r="B8" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="D8" s="80" t="s">
+      <c r="D8" s="72" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="81" t="s">
+      <c r="E8" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="G8" s="80" t="s">
+      <c r="G8" s="72" t="s">
         <v>154</v>
       </c>
-      <c r="H8" s="80" t="s">
+      <c r="H8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="I8" s="80" t="s">
+      <c r="I8" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="J8" s="81" t="s">
+      <c r="J8" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="K8" s="81" t="s">
+      <c r="K8" s="73" t="s">
         <v>157</v>
       </c>
-      <c r="M8" s="81" t="s">
+      <c r="M8" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="N8" s="81" t="s">
+      <c r="N8" s="73" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:23" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="70" t="s">
         <v>160</v>
       </c>
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="D9" s="78" t="s">
+      <c r="D9" s="70" t="s">
         <v>161</v>
       </c>
-      <c r="E9" s="79" t="s">
+      <c r="E9" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="G9" s="80" t="s">
+      <c r="G9" s="72" t="s">
         <v>162</v>
       </c>
-      <c r="H9" s="78">
+      <c r="H9" s="70">
         <v>2</v>
       </c>
-      <c r="I9" s="78">
+      <c r="I9" s="70">
         <v>0</v>
       </c>
-      <c r="J9" s="78">
+      <c r="J9" s="70">
         <v>0</v>
       </c>
-      <c r="K9" s="81">
+      <c r="K9" s="73">
         <f>(H9*4)+(I9*6)+(J9*8)</f>
         <v>8</v>
       </c>
-      <c r="M9" s="82" t="s">
+      <c r="M9" s="74" t="s">
         <v>163</v>
       </c>
-      <c r="N9" s="83"/>
+      <c r="N9" s="75"/>
     </row>
     <row r="10" spans="1:23" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="70" t="s">
         <v>164</v>
       </c>
-      <c r="B10" s="79" t="s">
+      <c r="B10" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="D10" s="78"/>
-      <c r="E10" s="79"/>
-      <c r="G10" s="80" t="s">
+      <c r="D10" s="70"/>
+      <c r="E10" s="71"/>
+      <c r="G10" s="72" t="s">
         <v>165</v>
       </c>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="78"/>
-      <c r="K10" s="81">
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="73">
         <f>(H10*3)+(I10*4)+(J10*6)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="82" t="s">
+      <c r="M10" s="74" t="s">
         <v>166</v>
       </c>
-      <c r="N10" s="83"/>
+      <c r="N10" s="75"/>
     </row>
     <row r="11" spans="1:23" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="78"/>
-      <c r="B11" s="79"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="79"/>
-      <c r="G11" s="152" t="s">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="71"/>
+      <c r="G11" s="141" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="152"/>
-      <c r="I11" s="152"/>
-      <c r="J11" s="152"/>
-      <c r="K11" s="152"/>
-      <c r="M11" s="82" t="s">
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="141"/>
+      <c r="K11" s="141"/>
+      <c r="M11" s="74" t="s">
         <v>168</v>
       </c>
-      <c r="N11" s="83"/>
+      <c r="N11" s="75"/>
     </row>
     <row r="12" spans="1:23" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A12" s="78"/>
-      <c r="B12" s="79"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="79"/>
-      <c r="G12" s="80" t="s">
+      <c r="A12" s="70"/>
+      <c r="B12" s="71"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="71"/>
+      <c r="G12" s="72" t="s">
         <v>154</v>
       </c>
-      <c r="H12" s="80" t="s">
+      <c r="H12" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="I12" s="80" t="s">
+      <c r="I12" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="J12" s="81" t="s">
+      <c r="J12" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="K12" s="81" t="s">
+      <c r="K12" s="73" t="s">
         <v>157</v>
       </c>
-      <c r="M12" s="82" t="s">
+      <c r="M12" s="74" t="s">
         <v>169</v>
       </c>
-      <c r="N12" s="83"/>
+      <c r="N12" s="75"/>
     </row>
     <row r="13" spans="1:23" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A13" s="78"/>
-      <c r="B13" s="79"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="79"/>
-      <c r="G13" s="80" t="s">
+      <c r="A13" s="70"/>
+      <c r="B13" s="71"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="71"/>
+      <c r="G13" s="72" t="s">
         <v>170</v>
       </c>
-      <c r="H13" s="78">
+      <c r="H13" s="70">
         <v>1</v>
       </c>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="81">
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="73">
         <f>(H13*3)+(I13*4)+(J13*6)</f>
         <v>3</v>
       </c>
-      <c r="M13" s="82" t="s">
+      <c r="M13" s="74" t="s">
         <v>171</v>
       </c>
-      <c r="N13" s="83"/>
+      <c r="N13" s="75"/>
       <c r="W13" s="4" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:23" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A14" s="78"/>
-      <c r="B14" s="79"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="79"/>
-      <c r="G14" s="80" t="s">
+      <c r="A14" s="70"/>
+      <c r="B14" s="71"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="71"/>
+      <c r="G14" s="72" t="s">
         <v>173</v>
       </c>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="81">
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="73">
         <f>(H14*4)+(I14*5)+(J14*7)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="82" t="s">
+      <c r="M14" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="N14" s="83"/>
+      <c r="N14" s="75"/>
     </row>
     <row r="15" spans="1:23" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A15" s="78"/>
-      <c r="B15" s="79"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="79"/>
-      <c r="G15" s="80" t="s">
+      <c r="A15" s="70"/>
+      <c r="B15" s="71"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="71"/>
+      <c r="G15" s="72" t="s">
         <v>175</v>
       </c>
-      <c r="H15" s="78">
+      <c r="H15" s="70">
         <v>1</v>
       </c>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="81">
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="73">
         <f>(H15*3)+(I15*4)+(J15*6)</f>
         <v>3</v>
       </c>
-      <c r="M15" s="82" t="s">
+      <c r="M15" s="74" t="s">
         <v>176</v>
       </c>
-      <c r="N15" s="83"/>
+      <c r="N15" s="75"/>
     </row>
     <row r="16" spans="1:23" s="4" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="78"/>
-      <c r="B16" s="79"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="79"/>
-      <c r="G16" s="153" t="s">
+      <c r="A16" s="70"/>
+      <c r="B16" s="71"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="71"/>
+      <c r="G16" s="142" t="s">
         <v>177</v>
       </c>
-      <c r="H16" s="153"/>
-      <c r="I16" s="153"/>
-      <c r="J16" s="153"/>
-      <c r="K16" s="84">
+      <c r="H16" s="142"/>
+      <c r="I16" s="142"/>
+      <c r="J16" s="142"/>
+      <c r="K16" s="76">
         <f>SUM(K9,K10,K13,K14,K15)</f>
         <v>14</v>
       </c>
-      <c r="M16" s="82" t="s">
+      <c r="M16" s="74" t="s">
         <v>178</v>
       </c>
-      <c r="N16" s="83"/>
+      <c r="N16" s="75"/>
     </row>
     <row r="17" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A17" s="78"/>
-      <c r="B17" s="79"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="79"/>
-      <c r="M17" s="82" t="s">
+      <c r="A17" s="70"/>
+      <c r="B17" s="71"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="71"/>
+      <c r="M17" s="74" t="s">
         <v>179</v>
       </c>
-      <c r="N17" s="83"/>
+      <c r="N17" s="75"/>
     </row>
     <row r="18" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A18" s="78"/>
-      <c r="B18" s="79"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="79"/>
-      <c r="M18" s="82" t="s">
+      <c r="A18" s="70"/>
+      <c r="B18" s="71"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="71"/>
+      <c r="M18" s="74" t="s">
         <v>180</v>
       </c>
-      <c r="N18" s="83"/>
+      <c r="N18" s="75"/>
     </row>
     <row r="19" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A19" s="78"/>
-      <c r="B19" s="79"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="79"/>
-      <c r="M19" s="82" t="s">
+      <c r="A19" s="70"/>
+      <c r="B19" s="71"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="71"/>
+      <c r="M19" s="74" t="s">
         <v>181</v>
       </c>
-      <c r="N19" s="83"/>
+      <c r="N19" s="75"/>
     </row>
     <row r="20" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="78"/>
-      <c r="B20" s="79"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="79"/>
-      <c r="M20" s="82" t="s">
+      <c r="A20" s="70"/>
+      <c r="B20" s="71"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="71"/>
+      <c r="M20" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="N20" s="83"/>
+      <c r="N20" s="75"/>
     </row>
     <row r="21" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="M21" s="82" t="s">
+      <c r="M21" s="74" t="s">
         <v>183</v>
       </c>
-      <c r="N21" s="83"/>
+      <c r="N21" s="75"/>
     </row>
     <row r="22" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="M22" s="82" t="s">
+      <c r="M22" s="74" t="s">
         <v>184</v>
       </c>
-      <c r="N22" s="83"/>
+      <c r="N22" s="75"/>
     </row>
     <row r="23" spans="1:14" s="4" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="M23" s="85" t="s">
+      <c r="M23" s="77" t="s">
         <v>185</v>
       </c>
-      <c r="N23" s="86">
+      <c r="N23" s="78">
         <f>SUM(N9:N22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M24" s="85" t="s">
+      <c r="M24" s="77" t="s">
         <v>186</v>
       </c>
-      <c r="N24" s="84">
+      <c r="N24" s="76">
         <f>(N23*0.01)+0.65</f>
         <v>0.65</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M25" s="85" t="s">
+      <c r="M25" s="77" t="s">
         <v>187</v>
       </c>
-      <c r="N25" s="87">
+      <c r="N25" s="79">
         <f>K16*N24</f>
         <v>9.1</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M26" s="85" t="s">
+      <c r="M26" s="77" t="s">
         <v>188</v>
       </c>
-      <c r="N26" s="88">
+      <c r="N26" s="80">
         <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="21" x14ac:dyDescent="0.3">
-      <c r="M27" s="89" t="s">
+      <c r="M27" s="81" t="s">
         <v>189</v>
       </c>
-      <c r="N27" s="90">
+      <c r="N27" s="82">
         <f>N25*N26</f>
         <v>172.9</v>
       </c>
@@ -11376,74 +11369,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="143" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="154"/>
-      <c r="K1" s="154"/>
-      <c r="L1" s="154"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="154"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="143"/>
+      <c r="L1" s="143"/>
+      <c r="M1" s="143"/>
+      <c r="N1" s="143"/>
     </row>
     <row r="2" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="160" t="s">
+      <c r="A3" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="160"/>
-      <c r="C3" s="160"/>
-      <c r="E3" s="160" t="s">
+      <c r="B3" s="149"/>
+      <c r="C3" s="149"/>
+      <c r="E3" s="149" t="s">
         <v>190</v>
       </c>
-      <c r="F3" s="160"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="160"/>
+      <c r="F3" s="149"/>
+      <c r="G3" s="149"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
+      <c r="K3" s="149"/>
+      <c r="L3" s="149"/>
+      <c r="M3" s="149"/>
+      <c r="N3" s="149"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="83" t="s">
         <v>191</v>
       </c>
-      <c r="B4" s="92">
+      <c r="B4" s="84">
         <f>'#Estimativa-APF#'!$N$27</f>
         <v>172.9</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="161" t="s">
+      <c r="E4" s="150" t="s">
         <v>192</v>
       </c>
-      <c r="F4" s="159" t="s">
+      <c r="F4" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="159"/>
-      <c r="H4" s="159" t="s">
+      <c r="G4" s="148"/>
+      <c r="H4" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="159"/>
-      <c r="J4" s="159" t="s">
+      <c r="I4" s="148"/>
+      <c r="J4" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="159"/>
-      <c r="L4" s="159" t="s">
+      <c r="K4" s="148"/>
+      <c r="L4" s="148" t="s">
         <v>40</v>
       </c>
-      <c r="M4" s="159"/>
-      <c r="N4" s="93"/>
+      <c r="M4" s="148"/>
+      <c r="N4" s="85"/>
     </row>
     <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
@@ -11455,68 +11448,68 @@
       <c r="C5" s="35" t="s">
         <v>193</v>
       </c>
-      <c r="E5" s="161"/>
-      <c r="F5" s="159" t="s">
+      <c r="E5" s="150"/>
+      <c r="F5" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="159"/>
-      <c r="H5" s="159" t="s">
+      <c r="G5" s="148"/>
+      <c r="H5" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="159"/>
-      <c r="J5" s="159" t="s">
+      <c r="I5" s="148"/>
+      <c r="J5" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="159"/>
-      <c r="L5" s="159" t="s">
+      <c r="K5" s="148"/>
+      <c r="L5" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="M5" s="159"/>
+      <c r="M5" s="148"/>
       <c r="N5" s="38" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="86" t="s">
         <v>195</v>
       </c>
-      <c r="B6" s="95">
+      <c r="B6" s="87">
         <f>B4+(B4*B5)</f>
         <v>172.9</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="161"/>
-      <c r="F6" s="96">
+      <c r="E6" s="150"/>
+      <c r="F6" s="88">
         <f>B6*G6</f>
         <v>8.6450000000000014</v>
       </c>
-      <c r="G6" s="97">
+      <c r="G6" s="89">
         <v>0.05</v>
       </c>
-      <c r="H6" s="96">
+      <c r="H6" s="88">
         <f>B4*I6</f>
         <v>34.580000000000005</v>
       </c>
-      <c r="I6" s="97">
+      <c r="I6" s="89">
         <v>0.2</v>
       </c>
-      <c r="J6" s="96">
+      <c r="J6" s="88">
         <f>B4*K6</f>
         <v>112.38500000000001</v>
       </c>
-      <c r="K6" s="97">
+      <c r="K6" s="89">
         <v>0.65</v>
       </c>
-      <c r="L6" s="96">
+      <c r="L6" s="88">
         <f>B4*M6</f>
         <v>17.290000000000003</v>
       </c>
-      <c r="M6" s="97">
+      <c r="M6" s="89">
         <v>0.1</v>
       </c>
-      <c r="N6" s="96"/>
+      <c r="N6" s="88"/>
     </row>
     <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
@@ -11526,38 +11519,38 @@
         <v>1</v>
       </c>
       <c r="C7" s="27"/>
-      <c r="E7" s="98" t="s">
+      <c r="E7" s="90" t="s">
         <v>197</v>
       </c>
-      <c r="F7" s="96">
+      <c r="F7" s="88">
         <f>F6*G7</f>
         <v>4.7547500000000014</v>
       </c>
-      <c r="G7" s="97">
+      <c r="G7" s="89">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H7" s="96">
+      <c r="H7" s="88">
         <f>H6*I7</f>
         <v>10.374000000000001</v>
       </c>
-      <c r="I7" s="97">
+      <c r="I7" s="89">
         <v>0.3</v>
       </c>
-      <c r="J7" s="96">
+      <c r="J7" s="88">
         <f>J6*K7</f>
         <v>13.4862</v>
       </c>
-      <c r="K7" s="97">
+      <c r="K7" s="89">
         <v>0.12</v>
       </c>
-      <c r="L7" s="96">
+      <c r="L7" s="88">
         <f>L6*M7</f>
         <v>0.86450000000000016</v>
       </c>
-      <c r="M7" s="97">
+      <c r="M7" s="89">
         <v>0.05</v>
       </c>
-      <c r="N7" s="99">
+      <c r="N7" s="91">
         <f>SUM(F7,H7,J7,L7)</f>
         <v>29.47945</v>
       </c>
@@ -11572,38 +11565,38 @@
       <c r="C8" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="E8" s="98" t="s">
+      <c r="E8" s="90" t="s">
         <v>200</v>
       </c>
-      <c r="F8" s="96">
+      <c r="F8" s="88">
         <f>F6*G8</f>
         <v>1.2967500000000001</v>
       </c>
-      <c r="G8" s="97">
+      <c r="G8" s="89">
         <v>0.15</v>
       </c>
-      <c r="H8" s="96">
+      <c r="H8" s="88">
         <f>H6*I8</f>
         <v>6.9160000000000013</v>
       </c>
-      <c r="I8" s="97">
+      <c r="I8" s="89">
         <v>0.2</v>
       </c>
-      <c r="J8" s="96">
+      <c r="J8" s="88">
         <f>J6*K8</f>
         <v>11.238500000000002</v>
       </c>
-      <c r="K8" s="97">
+      <c r="K8" s="89">
         <v>0.1</v>
       </c>
-      <c r="L8" s="96">
+      <c r="L8" s="88">
         <f>L6*M8</f>
         <v>0.86450000000000016</v>
       </c>
-      <c r="M8" s="97">
+      <c r="M8" s="89">
         <v>0.05</v>
       </c>
-      <c r="N8" s="99">
+      <c r="N8" s="91">
         <f>SUM(F8,H8,J8,L8)</f>
         <v>20.315750000000001</v>
       </c>
@@ -11618,348 +11611,348 @@
       <c r="C9" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="98" t="s">
+      <c r="E9" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="F9" s="96">
+      <c r="F9" s="88">
         <f>F6*G9</f>
         <v>0.17290000000000003</v>
       </c>
-      <c r="G9" s="97">
+      <c r="G9" s="89">
         <v>0.02</v>
       </c>
-      <c r="H9" s="96">
+      <c r="H9" s="88">
         <f>H6*I9</f>
         <v>6.9160000000000013</v>
       </c>
-      <c r="I9" s="97">
+      <c r="I9" s="89">
         <v>0.2</v>
       </c>
-      <c r="J9" s="96">
+      <c r="J9" s="88">
         <f>J6*K9</f>
         <v>44.954000000000008</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="89">
         <v>0.4</v>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="88">
         <f>L6*M9</f>
         <v>2.5935000000000001</v>
       </c>
-      <c r="M9" s="97">
+      <c r="M9" s="89">
         <v>0.15</v>
       </c>
-      <c r="N9" s="99">
+      <c r="N9" s="91">
         <f>SUM(F9,H9,J9,L9)</f>
         <v>54.636400000000009</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="100" t="s">
+      <c r="A10" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="B10" s="101">
+      <c r="B10" s="93">
         <f>(B7*B8)*B9</f>
         <v>80</v>
       </c>
-      <c r="C10" s="100" t="s">
+      <c r="C10" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="98" t="s">
+      <c r="E10" s="90" t="s">
         <v>204</v>
       </c>
-      <c r="F10" s="96">
+      <c r="F10" s="88">
         <f>F6*G10</f>
         <v>0.43225000000000008</v>
       </c>
-      <c r="G10" s="97">
+      <c r="G10" s="89">
         <v>0.05</v>
       </c>
-      <c r="H10" s="96">
+      <c r="H10" s="88">
         <f>H6*I10</f>
         <v>2.7664000000000004</v>
       </c>
-      <c r="I10" s="97">
+      <c r="I10" s="89">
         <v>0.08</v>
       </c>
-      <c r="J10" s="96">
+      <c r="J10" s="88">
         <f>J6*K10</f>
         <v>11.238500000000002</v>
       </c>
-      <c r="K10" s="97">
+      <c r="K10" s="89">
         <v>0.1</v>
       </c>
-      <c r="L10" s="96">
+      <c r="L10" s="88">
         <f>L6*M10</f>
         <v>1.7290000000000003</v>
       </c>
-      <c r="M10" s="97">
+      <c r="M10" s="89">
         <v>0.1</v>
       </c>
-      <c r="N10" s="99">
+      <c r="N10" s="91">
         <f>SUM(F10,H10,J10,L10)</f>
         <v>16.166150000000002</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="91" t="s">
+      <c r="A11" s="83" t="s">
         <v>205</v>
       </c>
-      <c r="B11" s="102">
+      <c r="B11" s="94">
         <f>B6/B10*2</f>
         <v>4.3224999999999998</v>
       </c>
-      <c r="C11" s="91" t="s">
+      <c r="C11" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="98" t="s">
+      <c r="E11" s="90" t="s">
         <v>206</v>
       </c>
-      <c r="F11" s="96">
+      <c r="F11" s="88">
         <f>F6*G11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="97">
+      <c r="G11" s="89">
         <v>0</v>
       </c>
-      <c r="H11" s="96">
+      <c r="H11" s="88">
         <f>H6*I11</f>
         <v>0.6916000000000001</v>
       </c>
-      <c r="I11" s="97">
+      <c r="I11" s="89">
         <v>0.02</v>
       </c>
-      <c r="J11" s="96">
+      <c r="J11" s="88">
         <f>J6*K11</f>
         <v>5.619250000000001</v>
       </c>
-      <c r="K11" s="97">
+      <c r="K11" s="89">
         <v>0.05</v>
       </c>
-      <c r="L11" s="96">
+      <c r="L11" s="88">
         <f>L6*M11</f>
         <v>1.7290000000000003</v>
       </c>
-      <c r="M11" s="97">
+      <c r="M11" s="89">
         <v>0.1</v>
       </c>
-      <c r="N11" s="99">
+      <c r="N11" s="91">
         <f>SUM(F11,H11,J11,L11)</f>
         <v>8.0398500000000013</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="91" t="s">
+      <c r="A12" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="B12" s="102">
+      <c r="B12" s="94">
         <f>B11/4</f>
         <v>1.0806249999999999</v>
       </c>
-      <c r="C12" s="91" t="s">
+      <c r="C12" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="103" t="s">
+      <c r="E12" s="95" t="s">
         <v>208</v>
       </c>
-      <c r="F12" s="104">
+      <c r="F12" s="96">
         <f t="shared" ref="F12:M12" si="0">SUM(F7:F11)</f>
         <v>6.6566500000000017</v>
       </c>
-      <c r="G12" s="105">
+      <c r="G12" s="97">
         <f t="shared" si="0"/>
         <v>0.77000000000000013</v>
       </c>
-      <c r="H12" s="104">
+      <c r="H12" s="96">
         <f t="shared" si="0"/>
         <v>27.664000000000005</v>
       </c>
-      <c r="I12" s="105">
+      <c r="I12" s="97">
         <f t="shared" si="0"/>
         <v>0.79999999999999993</v>
       </c>
-      <c r="J12" s="104">
+      <c r="J12" s="96">
         <f t="shared" si="0"/>
         <v>86.536450000000002</v>
       </c>
-      <c r="K12" s="105">
+      <c r="K12" s="97">
         <f t="shared" si="0"/>
         <v>0.77</v>
       </c>
-      <c r="L12" s="104">
+      <c r="L12" s="96">
         <f t="shared" si="0"/>
         <v>7.7805000000000009</v>
       </c>
-      <c r="M12" s="105">
+      <c r="M12" s="97">
         <f t="shared" si="0"/>
         <v>0.44999999999999996</v>
       </c>
-      <c r="N12" s="103"/>
+      <c r="N12" s="95"/>
     </row>
     <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="100" t="s">
+      <c r="A13" s="92" t="s">
         <v>209</v>
       </c>
-      <c r="B13" s="106">
+      <c r="B13" s="98">
         <f>B11/B9</f>
         <v>2.1612499999999999</v>
       </c>
-      <c r="C13" s="100" t="s">
+      <c r="C13" s="92" t="s">
         <v>210</v>
       </c>
-      <c r="E13" s="98" t="s">
+      <c r="E13" s="90" t="s">
         <v>211</v>
       </c>
-      <c r="F13" s="96">
+      <c r="F13" s="88">
         <f>F6*G13</f>
         <v>0.25935000000000002</v>
       </c>
-      <c r="G13" s="97">
+      <c r="G13" s="89">
         <v>0.03</v>
       </c>
-      <c r="H13" s="96">
+      <c r="H13" s="88">
         <f>H6*I13</f>
         <v>2.7664000000000004</v>
       </c>
-      <c r="I13" s="97">
+      <c r="I13" s="89">
         <v>0.08</v>
       </c>
-      <c r="J13" s="96">
+      <c r="J13" s="88">
         <f>J6*K13</f>
         <v>14.610050000000001</v>
       </c>
-      <c r="K13" s="97">
+      <c r="K13" s="89">
         <v>0.13</v>
       </c>
-      <c r="L13" s="96">
+      <c r="L13" s="88">
         <f>L6*M13</f>
         <v>5.1870000000000003</v>
       </c>
-      <c r="M13" s="97">
+      <c r="M13" s="89">
         <v>0.3</v>
       </c>
-      <c r="N13" s="99">
+      <c r="N13" s="91">
         <f>SUM(F13,H13,J13,L13)</f>
         <v>22.822800000000004</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E14" s="98" t="s">
+      <c r="E14" s="90" t="s">
         <v>212</v>
       </c>
-      <c r="F14" s="96">
+      <c r="F14" s="88">
         <f>F6*G14</f>
         <v>1.7290000000000003</v>
       </c>
-      <c r="G14" s="97">
+      <c r="G14" s="89">
         <v>0.2</v>
       </c>
-      <c r="H14" s="96">
+      <c r="H14" s="88">
         <f>H6*I14</f>
         <v>4.1496000000000004</v>
       </c>
-      <c r="I14" s="97">
+      <c r="I14" s="89">
         <v>0.12</v>
       </c>
-      <c r="J14" s="96">
+      <c r="J14" s="88">
         <f>J6*K14</f>
         <v>11.238500000000002</v>
       </c>
-      <c r="K14" s="97">
+      <c r="K14" s="89">
         <v>0.1</v>
       </c>
-      <c r="L14" s="96">
+      <c r="L14" s="88">
         <f>L6*M14</f>
         <v>4.3225000000000007</v>
       </c>
-      <c r="M14" s="97">
+      <c r="M14" s="89">
         <v>0.25</v>
       </c>
-      <c r="N14" s="99">
+      <c r="N14" s="91">
         <f>SUM(F14,H14,J14,L14)</f>
         <v>21.439600000000002</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="E15" s="103" t="s">
+      <c r="E15" s="95" t="s">
         <v>213</v>
       </c>
-      <c r="F15" s="104">
+      <c r="F15" s="96">
         <f t="shared" ref="F15:M15" si="1">SUM(F13:F14)</f>
         <v>1.9883500000000003</v>
       </c>
-      <c r="G15" s="105">
+      <c r="G15" s="97">
         <f t="shared" si="1"/>
         <v>0.23</v>
       </c>
-      <c r="H15" s="104">
+      <c r="H15" s="96">
         <f t="shared" si="1"/>
         <v>6.9160000000000004</v>
       </c>
-      <c r="I15" s="105">
+      <c r="I15" s="97">
         <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
-      <c r="J15" s="104">
+      <c r="J15" s="96">
         <f t="shared" si="1"/>
         <v>25.848550000000003</v>
       </c>
-      <c r="K15" s="105">
+      <c r="K15" s="97">
         <f t="shared" si="1"/>
         <v>0.23</v>
       </c>
-      <c r="L15" s="104">
+      <c r="L15" s="96">
         <f t="shared" si="1"/>
         <v>9.509500000000001</v>
       </c>
-      <c r="M15" s="105">
+      <c r="M15" s="97">
         <f t="shared" si="1"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="N15" s="103"/>
+      <c r="N15" s="95"/>
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="160" t="s">
+      <c r="A16" s="149" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="160"/>
-      <c r="C16" s="160"/>
+      <c r="B16" s="149"/>
+      <c r="C16" s="149"/>
       <c r="E16" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="F16" s="107">
+      <c r="F16" s="99">
         <f t="shared" ref="F16:M16" si="2">F12+F15</f>
         <v>8.6450000000000014</v>
       </c>
-      <c r="G16" s="108">
+      <c r="G16" s="100">
         <f t="shared" si="2"/>
         <v>1.0000000000000002</v>
       </c>
-      <c r="H16" s="107">
+      <c r="H16" s="99">
         <f t="shared" si="2"/>
         <v>34.580000000000005</v>
       </c>
-      <c r="I16" s="108">
+      <c r="I16" s="100">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="J16" s="107">
+      <c r="J16" s="99">
         <f t="shared" si="2"/>
         <v>112.38500000000001</v>
       </c>
-      <c r="K16" s="108">
+      <c r="K16" s="100">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L16" s="107">
+      <c r="L16" s="99">
         <f t="shared" si="2"/>
         <v>17.290000000000003</v>
       </c>
-      <c r="M16" s="108">
+      <c r="M16" s="100">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N16" s="109">
+      <c r="N16" s="101">
         <f>SUM(N7:N11,N13,N14)</f>
         <v>172.90000000000003</v>
       </c>
@@ -11968,11 +11961,11 @@
       <c r="A17" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="110">
+      <c r="B17" s="102">
         <v>20</v>
       </c>
       <c r="C17" s="35"/>
-      <c r="N17" s="58"/>
+      <c r="N17" s="51"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
@@ -11983,8 +11976,8 @@
         <v>3458</v>
       </c>
       <c r="C18" s="35"/>
-      <c r="L18" s="58"/>
-      <c r="N18" s="58"/>
+      <c r="L18" s="51"/>
+      <c r="N18" s="51"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
@@ -11994,7 +11987,7 @@
         <v>0</v>
       </c>
       <c r="C19" s="35"/>
-      <c r="N19" s="58"/>
+      <c r="N19" s="51"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
@@ -12005,19 +11998,19 @@
         <v>0</v>
       </c>
       <c r="C20" s="35"/>
-      <c r="L20" s="58"/>
-      <c r="N20" s="58"/>
+      <c r="L20" s="51"/>
+      <c r="N20" s="51"/>
     </row>
     <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="B21" s="111">
+      <c r="B21" s="103">
         <f>B18+B20</f>
         <v>3458</v>
       </c>
       <c r="C21" s="35"/>
-      <c r="N21" s="58"/>
+      <c r="N21" s="51"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="s">
@@ -12027,7 +12020,7 @@
         <v>0.2</v>
       </c>
       <c r="C22" s="35"/>
-      <c r="J22" s="58"/>
+      <c r="J22" s="51"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="27" t="s">
@@ -12043,23 +12036,23 @@
       <c r="A24" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="B24" s="111">
+      <c r="B24" s="103">
         <f>B21+B23</f>
         <v>4149.6000000000004</v>
       </c>
       <c r="C24" s="35"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="J26" s="58"/>
+      <c r="J26" s="51"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="J27" s="58"/>
+      <c r="J27" s="51"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N28" s="58"/>
+      <c r="N28" s="51"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N29" s="58"/>
+      <c r="N29" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="13">
